--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484728_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484728_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7691</v>
+        <v>3.0879</v>
       </c>
       <c r="E2" t="n">
-        <v>3.275</v>
+        <v>3.5673</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5059</v>
+        <v>-0.4795</v>
       </c>
       <c r="G2" t="n">
         <v>0.7175</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.137</v>
+        <v>0.1818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1451</v>
+        <v>0.4374</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2821</v>
+        <v>-0.2556</v>
       </c>
       <c r="V2" t="n">
         <v>2.1886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7126</v>
+        <v>2.4392</v>
       </c>
       <c r="E3" t="n">
-        <v>1.819</v>
+        <v>1.3514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.0879</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0823</v>
+        <v>1.1277</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5387</v>
+        <v>-0.6996</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4564</v>
+        <v>1.8273</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0525</v>
+        <v>2.1033</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0114</v>
+        <v>0.2113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0411</v>
+        <v>1.892</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9702</v>
+        <v>-0.9756</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4727</v>
+        <v>-0.9109</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4976</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.5853</v>
+        <v>0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.9062</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4044</v>
+        <v>0.4926</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5031</v>
+        <v>0.1916</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0987</v>
+        <v>0.301</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8112</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.354</v>
+        <v>2.1646</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2926</v>
+        <v>-0.1007</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0614</v>
+        <v>2.2653</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1277</v>
+        <v>1.2348</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6996</v>
+        <v>1.0377</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8273</v>
+        <v>0.1971</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1033</v>
+        <v>1.6256</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2113</v>
+        <v>0.9093</v>
       </c>
       <c r="L4" t="n">
-        <v>1.892</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9756</v>
+        <v>-0.3908</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9109</v>
+        <v>0.1284</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.5191</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7548</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4074</v>
+        <v>0.1865</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1328</v>
+        <v>-0.141</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2746</v>
+        <v>0.3275</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06419999999999999</v>
+        <v>1.3094</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
         <v>0.06419999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3355</v>
+        <v>2.128</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.062</v>
+        <v>1.2344</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3976</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2348</v>
+        <v>2.0823</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0377</v>
+        <v>2.5387</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1971</v>
+        <v>-0.4564</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6256</v>
+        <v>3.0525</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9093</v>
+        <v>3.0114</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.0411</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3908</v>
+        <v>-0.9702</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1284</v>
+        <v>-0.4727</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5191</v>
+        <v>-0.4976</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5661</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-4.9062</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3574</v>
+        <v>0.8198</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1023</v>
+        <v>0.9185</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4598</v>
+        <v>-0.0987</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3094</v>
+        <v>2.8112</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>2.1696</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PEREZ DIEZ</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2251</v>
+        <v>2.1091</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0912</v>
+        <v>1.3862</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1339</v>
+        <v>0.7229</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6737</v>
+        <v>-2.8233</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6582</v>
+        <v>-1.4314</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0156</v>
+        <v>-1.3919</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0292</v>
+        <v>-1.8584</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1526</v>
+        <v>-1.2671</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1234</v>
+        <v>-0.5914</v>
       </c>
       <c r="M6" t="n">
-        <v>0.703</v>
+        <v>-0.9648</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8108</v>
+        <v>-0.1643</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1078</v>
+        <v>-0.8005</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>2.4531</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6079</v>
+        <v>0.5855</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3092</v>
+        <v>0.1698</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2987</v>
+        <v>0.4157</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.7808</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.9618</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>M. PEREZ DIEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.74</v>
+        <v>1.6515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9377</v>
+        <v>-0.0062</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8023</v>
+        <v>1.6577</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8233</v>
+        <v>0.6737</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4314</v>
+        <v>0.6582</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3919</v>
+        <v>0.0156</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8584</v>
+        <v>-0.0292</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2671</v>
+        <v>-0.1526</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5914</v>
+        <v>0.1234</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9648</v>
+        <v>0.703</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1643</v>
+        <v>0.8108</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8005</v>
+        <v>-0.1078</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4531</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2164</v>
+        <v>0.0343</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2787</v>
+        <v>0.2117</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4951</v>
+        <v>-0.1774</v>
       </c>
       <c r="V7" t="n">
-        <v>3.7808</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.9618</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3248</v>
+        <v>1.2971</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2189</v>
+        <v>1.9266</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.894</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.249</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2722</v>
+        <v>0.2444</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0763</v>
+        <v>0.784</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8041</v>
+        <v>-0.5396</v>
       </c>
       <c r="V8" t="n">
         <v>1.8678</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6339</v>
+        <v>0.6899</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6339</v>
+        <v>-0.504</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.1939</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6339</v>
+        <v>1.4221</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6339</v>
+        <v>2.9113</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1.4892</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6339</v>
+        <v>1.6074</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6339</v>
+        <v>2.8158</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.2083</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.1854</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.0955</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.2809</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.4189</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.0357</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.3832</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3053</v>
+        <v>0.6339</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4654</v>
+        <v>0.6339</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7706</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4221</v>
+        <v>0.6339</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9113</v>
+        <v>0.6339</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4892</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6074</v>
+        <v>0.6339</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8158</v>
+        <v>0.6339</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2083</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1854</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0955</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2809</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8036</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8065</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. SELLER BERNABE</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2073</v>
+        <v>-1.0123</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9435</v>
+        <v>0.293</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2638</v>
+        <v>-1.3053</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0216</v>
+        <v>-0.0154</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0216</v>
+        <v>-2.1042</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.1887</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2.8212</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.6325</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0216</v>
+        <v>-2.2041</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.7325</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0216</v>
+        <v>-1.4716</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2422</v>
+        <v>0.2221</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.0292</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2422</v>
+        <v>0.1929</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>F. SELLER BERNABE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4789</v>
+        <v>-1.1808</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.253</v>
+        <v>-0.9435</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2259</v>
+        <v>-0.2373</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0154</v>
+        <v>-0.0216</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0887</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1042</v>
+        <v>-0.0216</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1887</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8212</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6325</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2041</v>
+        <v>-0.0216</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7325</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4716</v>
+        <v>-0.0216</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R13" t="n">
-        <v>1.887</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2445</v>
+        <v>-0.2157</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5168</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2722</v>
+        <v>-0.2157</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.219</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.7706</v>
+        <v>13.0646</v>
       </c>
       <c r="E14" t="n">
-        <v>7.600899999999998</v>
+        <v>7.8949</v>
       </c>
       <c r="F14" t="n">
-        <v>5.1698</v>
+        <v>5.1697</v>
       </c>
       <c r="G14" t="n">
         <v>5.0425</v>
@@ -1537,7 +1537,7 @@
         <v>-3.6765</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.7175</v>
+        <v>-4.717500000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-18.87</v>
@@ -1546,13 +1546,13 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>1.578600000000001</v>
+        <v>1.8726</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2716</v>
+        <v>2.5655</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6930000000000001</v>
+        <v>-0.6929</v>
       </c>
       <c r="V14" t="n">
         <v>10.8672</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6514</v>
+        <v>1.5142</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5302</v>
+        <v>1.9456</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8788</v>
+        <v>-0.4314</v>
       </c>
       <c r="G15" t="n">
         <v>1.0314</v>
@@ -1624,13 +1624,13 @@
         <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6536</v>
+        <v>0.5164</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0328</v>
+        <v>0.4482</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3791</v>
+        <v>0.0682</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5432</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.3029</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0793</v>
+        <v>0.5053</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6171</v>
+        <v>0.7976</v>
       </c>
       <c r="G16" t="n">
         <v>0.6031</v>
@@ -1702,13 +1702,13 @@
         <v>2.4531</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5748</v>
+        <v>-0.8098</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0335</v>
+        <v>-0.4489</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5413</v>
+        <v>-0.3609</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>R. AMOROS PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3834</v>
+        <v>0.5916</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2642</v>
+        <v>-0.0731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6476</v>
+        <v>0.6647</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.6274</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0454</v>
+        <v>1.1363</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7564</v>
+        <v>1.8721</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5166</v>
+        <v>1.0565</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2397</v>
+        <v>0.8155</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0855</v>
+        <v>-0.2447</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.562</v>
+        <v>0.0798</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4765</v>
+        <v>-0.3245</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0757</v>
+        <v>-2.8305</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3966</v>
+        <v>2.8305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2557</v>
+        <v>-0.417</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0551</v>
+        <v>-0.039</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2005</v>
+        <v>-0.3779</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.864</v>
+        <v>-0.6188</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.864</v>
+        <v>-1.5432</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2217</v>
+        <v>0.2194</v>
       </c>
       <c r="E18" t="n">
         <v>1.011</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7893</v>
+        <v>-0.7916</v>
       </c>
       <c r="G18" t="n">
         <v>1.8822</v>
@@ -1858,13 +1858,13 @@
         <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7131</v>
+        <v>0.7107</v>
       </c>
       <c r="T18" t="n">
         <v>0.6989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0142</v>
+        <v>0.0118</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2414</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. AMOROS PEREZ</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0492</v>
+        <v>0.0804</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1705</v>
+        <v>-0.4591</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2197</v>
+        <v>0.5394</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6274</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1363</v>
+        <v>-0.0454</v>
       </c>
       <c r="I19" t="n">
-        <v>0.491</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8721</v>
+        <v>1.7564</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0565</v>
+        <v>1.5166</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8155</v>
+        <v>0.2397</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2447</v>
+        <v>-1.0855</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0798</v>
+        <v>-1.562</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3245</v>
+        <v>0.4765</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8305</v>
+        <v>-2.0757</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8305</v>
+        <v>3.3966</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9594</v>
+        <v>-0.0474</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1365</v>
+        <v>-0.1397</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8229</v>
+        <v>0.0924</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6188</v>
+        <v>-1.864</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5432</v>
+        <v>-1.864</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9865</v>
+        <v>-1.4375</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.326</v>
+        <v>-0.6183</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6605</v>
+        <v>-0.8192</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7923</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>0.485</v>
+        <v>0.0339</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3926</v>
+        <v>0.1003</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6226</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1894</v>
+        <v>-1.4508</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0976</v>
+        <v>-1.513</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.09180000000000001</v>
+        <v>0.0622</v>
       </c>
       <c r="G21" t="n">
         <v>-5.7996</v>
@@ -2092,13 +2092,13 @@
         <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5067</v>
+        <v>0.2319</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0052</v>
+        <v>0.1488</v>
       </c>
       <c r="V21" t="n">
         <v>2.796</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8005</v>
+        <v>-5.5972</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5815</v>
+        <v>-3.484</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.219</v>
+        <v>-2.1132</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7384</v>
@@ -2170,13 +2170,13 @@
         <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8359</v>
+        <v>-0.6327</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2569</v>
+        <v>-0.1595</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.579</v>
+        <v>-0.4732</v>
       </c>
       <c r="V22" t="n">
         <v>-3.4148</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6378</v>
+        <v>-6.6944</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1919</v>
+        <v>-2.4842</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4459</v>
+        <v>-4.2102</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5271</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.191</v>
+        <v>0.1344</v>
       </c>
       <c r="T23" t="n">
-        <v>0.442</v>
+        <v>0.1497</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.251</v>
+        <v>-0.0152</v>
       </c>
       <c r="V23" t="n">
         <v>-4.3582</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.7707</v>
+        <v>-11.4714</v>
       </c>
       <c r="E24" t="n">
         <v>-5.1698</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.600899999999999</v>
+        <v>-6.3017</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.042400000000001</v>
+        <v>-5.0424</v>
       </c>
       <c r="H24" t="n">
         <v>-7.6381</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5956</v>
+        <v>2.595600000000001</v>
       </c>
       <c r="J24" t="n">
         <v>5.2337</v>
@@ -2326,13 +2326,13 @@
         <v>18.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5784</v>
+        <v>-0.2796000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6929999999999998</v>
+        <v>0.6930999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2715</v>
+        <v>-0.9724</v>
       </c>
       <c r="V24" t="n">
         <v>-10.867</v>
